--- a/data/reports/PHASE_7_ROLLING_ENGINE.xlsx
+++ b/data/reports/PHASE_7_ROLLING_ENGINE.xlsx
@@ -446,11 +446,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -466,11 +466,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -496,27 +496,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>078</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -612,7 +612,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -622,7 +622,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -632,7 +632,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -642,7 +642,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -682,7 +682,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -712,7 +712,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>078</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -722,11 +722,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>026</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -772,7 +772,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>057</t>
+          <t>058</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -782,7 +782,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>058</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -792,7 +792,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>049</t>
+          <t>046</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -802,7 +802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>046</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -862,7 +862,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>026</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -872,7 +872,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -882,7 +882,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -912,7 +912,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -922,7 +922,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -932,7 +932,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -942,7 +942,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -952,7 +952,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -962,7 +962,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>226</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1022,7 +1022,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1052,7 +1052,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1448,7 +1448,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1458,7 +1458,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1468,7 +1468,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>07</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1478,7 +1478,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1488,7 +1488,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1498,7 +1498,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1508,7 +1508,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1518,17 +1518,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1538,17 +1538,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1558,7 +1558,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1568,7 +1568,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1578,7 +1578,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1588,7 +1588,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1598,27 +1598,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1638,7 +1638,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1648,7 +1648,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1668,7 +1668,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1678,7 +1678,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1698,7 +1698,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>04</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1708,7 +1708,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1718,7 +1718,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1728,7 +1728,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1738,7 +1738,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>09</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1748,17 +1748,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>08</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1768,7 +1768,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1778,7 +1778,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1788,7 +1788,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>03</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1798,7 +1798,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>02</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1808,7 +1808,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1818,17 +1818,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1838,7 +1838,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1848,7 +1848,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1858,7 +1858,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1868,7 +1868,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1878,7 +1878,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1888,7 +1888,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1898,11 +1898,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1918,11 +1918,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2013,7 +2013,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>6</v>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="n">
         <v>6</v>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -2069,7 +2069,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
@@ -2077,15 +2077,15 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
@@ -2182,23 +2182,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2212,47 +2212,47 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2464,7 +2464,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>068</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2484,7 +2484,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2504,7 +2504,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2524,7 +2524,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2534,7 +2534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2544,7 +2544,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2564,7 +2564,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2594,7 +2594,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2604,7 +2604,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2664,7 +2664,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>678</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2684,7 +2684,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>389</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2754,7 +2754,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>238</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2824,7 +2824,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>058</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2834,7 +2834,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>058</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2844,7 +2844,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2864,7 +2864,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>046</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2874,7 +2874,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2884,7 +2884,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>024</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2934,7 +2934,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -2944,7 +2944,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2954,7 +2954,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>079</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -2964,7 +2964,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2994,7 +2994,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3014,7 +3014,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3024,7 +3024,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3034,7 +3034,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3044,7 +3044,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3054,7 +3054,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>099</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -3064,7 +3064,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>089</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3174,7 +3174,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>057</t>
+          <t>046</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -3184,7 +3184,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>049</t>
+          <t>259</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -3324,7 +3324,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -3424,7 +3424,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>577</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3434,7 +3434,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>558</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3444,7 +3444,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3570,7 +3570,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -3580,7 +3580,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -3590,7 +3590,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3600,7 +3600,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -3620,7 +3620,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -3630,7 +3630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3720,7 +3720,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -3730,7 +3730,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -3740,7 +3740,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>09</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -3750,7 +3750,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>05</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -3760,7 +3760,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -3770,21 +3770,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -3800,7 +3800,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -3810,17 +3810,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>02</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -3830,7 +3830,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3840,7 +3840,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -3850,7 +3850,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -3860,7 +3860,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -3870,11 +3870,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -3890,7 +3890,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -3900,27 +3900,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -3930,7 +3930,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>08</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -3940,7 +3940,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -3950,7 +3950,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -3960,7 +3960,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -3970,7 +3970,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -3980,17 +3980,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -4000,7 +4000,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>04</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -4010,7 +4010,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -4020,21 +4020,21 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -4050,11 +4050,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -4070,7 +4070,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -4181,7 +4181,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
         <v>10</v>
@@ -4197,10 +4197,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -4221,15 +4221,15 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="n">
         <v>8</v>
-      </c>
-      <c r="B14" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
         <v>7</v>
@@ -4368,7 +4368,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4378,7 +4378,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4388,7 +4388,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>078</t>
+          <t>068</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4398,7 +4398,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4408,7 +4408,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4418,7 +4418,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4428,7 +4428,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4438,7 +4438,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4448,7 +4448,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -4458,7 +4458,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -4468,7 +4468,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -4478,7 +4478,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4488,7 +4488,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -4498,7 +4498,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -4508,7 +4508,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -4518,7 +4518,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -4528,7 +4528,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>369</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -4538,7 +4538,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>389</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -4548,7 +4548,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -4626,7 +4626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4664,7 +4664,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4684,7 +4684,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>06</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4694,7 +4694,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4724,7 +4724,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4734,7 +4734,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>07</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4744,7 +4744,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>04</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4754,7 +4754,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4764,7 +4764,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -4774,7 +4774,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -4784,7 +4784,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -4794,7 +4794,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4804,7 +4804,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -4814,7 +4814,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -4834,7 +4834,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>03</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -4844,7 +4844,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>09</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -4854,7 +4854,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -4864,7 +4864,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -4874,7 +4874,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -4884,7 +4884,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -4894,17 +4894,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -4914,7 +4914,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>02</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -4924,7 +4924,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -4944,7 +4944,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -4954,7 +4954,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -4964,7 +4964,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -4974,7 +4974,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -4984,7 +4984,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>08</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -5004,7 +5004,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -5014,7 +5014,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -5024,7 +5024,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -5034,7 +5034,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -5044,10 +5044,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5062,7 +5072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5079,15 +5089,15 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
@@ -5095,7 +5105,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -5103,7 +5113,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B5" t="n">
         <v>3</v>
@@ -5119,7 +5129,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
@@ -5127,7 +5137,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -5135,7 +5145,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
@@ -5143,7 +5153,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -5151,7 +5161,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
@@ -5159,7 +5169,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -5167,7 +5177,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -5175,7 +5185,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
@@ -5183,7 +5193,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
@@ -5191,7 +5201,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
@@ -5199,7 +5209,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
@@ -5207,9 +5217,17 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>25</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5246,23 +5264,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5272,17 +5290,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5296,7 +5314,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -5312,21 +5330,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -5350,7 +5368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5408,7 +5426,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>389</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5418,7 +5436,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5428,27 +5446,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>046</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5458,7 +5476,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5468,7 +5486,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>026</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5478,7 +5496,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>045</t>
+          <t>078</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5488,7 +5506,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5498,7 +5516,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5508,7 +5526,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5528,7 +5546,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5538,7 +5556,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>078</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5548,7 +5566,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>046</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5558,7 +5576,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>067</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5568,7 +5586,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5578,7 +5596,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>026</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5588,7 +5606,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5598,7 +5616,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5608,7 +5626,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -5618,7 +5636,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5628,7 +5646,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -5638,7 +5656,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -5648,7 +5666,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -5658,7 +5676,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -5668,7 +5686,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5678,7 +5696,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -5688,7 +5706,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>267</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -5698,7 +5716,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -5708,7 +5726,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -5718,7 +5736,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -5728,7 +5746,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -5738,7 +5756,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>237</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -5748,7 +5766,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -5758,7 +5776,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -5768,7 +5786,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -5778,7 +5796,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>369</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -5788,7 +5806,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -5798,7 +5816,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -5808,7 +5826,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -5818,7 +5836,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -5828,7 +5846,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -5838,7 +5856,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -5848,7 +5866,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>558</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -5858,7 +5876,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>577</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -5868,7 +5886,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>588</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -5878,10 +5896,30 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>799</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B55" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5924,17 +5962,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5944,7 +5982,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5954,17 +5992,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5974,7 +6012,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5984,7 +6022,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6004,7 +6042,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6014,7 +6052,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>07</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6024,7 +6062,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6034,17 +6072,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -6054,7 +6092,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6064,7 +6102,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>04</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6084,7 +6122,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6094,7 +6132,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6104,7 +6142,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6114,7 +6152,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6124,17 +6162,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>05</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6144,7 +6182,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6154,7 +6192,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6164,7 +6202,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6174,7 +6212,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>08</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6194,7 +6232,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6204,7 +6242,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6214,7 +6252,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6224,7 +6262,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -6234,11 +6272,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -6254,7 +6292,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6264,7 +6302,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>09</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6284,7 +6322,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>03</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6294,7 +6332,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -6304,7 +6342,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -6314,7 +6352,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6324,7 +6362,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -6334,7 +6372,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -6344,7 +6382,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -6354,7 +6392,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -6364,17 +6402,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -6384,7 +6422,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -6394,7 +6432,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -6404,7 +6442,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>02</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -6452,7 +6490,7 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -6553,10 +6591,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6615,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
@@ -6585,7 +6623,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
@@ -6640,7 +6678,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -6650,13 +6688,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6666,17 +6704,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6700,7 +6738,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -6710,27 +6748,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
